--- a/www/download/COUNTRY.FRA.WIOD16.xlsx
+++ b/www/download/COUNTRY.FRA.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>França</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.729660707770886</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>0.778331257783313</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.75272303819012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>25.672</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>26.041</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>26.161</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>26.164</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26.192</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>26.376</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>26.667</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>27.042</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>27.167</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>26.861</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>26.892</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>27.107</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>27.197</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>27.197</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>27.295</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>23.346</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>23.743</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>23.874</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>23.875</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>23.889</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>24.035</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>24.295</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>24.649</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>24.757</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>24.435</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>24.403</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>24.517</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>24.518</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>24.462</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>24.545</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>36942.169</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>37340.115</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>36641.344</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>36570.573</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>37323.374</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>37483.283</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>37330.401</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>38311.492</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>38757.878</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>37873.733</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>38048.975</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>38433.573</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>38427.711</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>38056.003</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>38131.699</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33668.202</t>
+          <t>46474152139.3086</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>34113.125</t>
+          <t>45652810596.6853</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33486.152</t>
+          <t>44750290935.9167</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>33417.848</t>
+          <t>46821639462.5757</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>34100.736</t>
+          <t>50015283743.5912</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>34206.04</t>
+          <t>50204300674.6048</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>34052.701</t>
+          <t>51221301529.8962</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>34960.624</t>
+          <t>52328166013.4042</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>35343.671</t>
+          <t>53244317667.0064</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34475.606</t>
+          <t>50431060144.6107</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>34548.595</t>
+          <t>49244646785.0234</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>34785.535</t>
+          <t>54651176105.0416</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>34667.971</t>
+          <t>51142271548.0997</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>34252.927</t>
+          <t>49092753385.9767</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>34307.826</t>
+          <t>48487675798.1752</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>26372019422.9433</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>27083369713.2043</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>29137345758.1091</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>31913709631.4038</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>31904650621.8544</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>31826551472.4216</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>31004979476.3919</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>30607980534.1507</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>30088402273.5743</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>27782671305.8272</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>24640900755.363</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>26354262352.3306</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>24932499751.053</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>25625593052.0506</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>26566575475.4961</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1251373.82094646</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1210895.65716418</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1139790.51769755</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1036976.98477028</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>969188.060858393</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>933746.839686177</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>873527.569280088</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>760017.001384752</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>698761.197989409</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>786975.768092872</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>753282.860158587</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>736631.136962455</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>744763.736836862</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>692850.416194851</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>691057.831531839</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>137899.718840695</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>136521.605314358</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>134011.350210612</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>145294.935346976</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>163751.781584447</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>176126.123467909</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>185258.434589264</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>213956.184029368</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>235038.784023304</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>209206.490198855</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>230992.437461723</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>246729.977114625</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>239264.767864521</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>236314.132944385</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>237217.330237337</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>377619.503363528</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>367459.185064231</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>362356.700926086</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>412604.91369696</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>487282.135881158</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>525161.135479389</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>566037.174845553</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>652903.507556169</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>721068.649713558</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>621526.252211998</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>672378.611910563</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>792437.849108004</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>722538.055681103</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>692893.077507582</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>687523.208602251</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.276663779896549</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.259559846549244</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.149251969551157</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0471314173741828</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0688327668644435</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0747642586926291</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0982978081288117</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.142206162899013</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.174660943397491</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.240903209792108</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.402083281897906</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.319920646419602</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.390473131300679</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.336668655060023</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.291390605900415</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>226374.081285586</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>229768.994596295</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>250773.774176741</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>312515.530678866</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>359407.244995</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>376826.423698733</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>400725.747924333</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>461528.053784302</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>515519.923242585</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>512417.548349397</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>518780.941763942</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>564185.582932056</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>538051.92174602</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>563525.237645964</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>570936.160677758</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>1129.61618362646</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>1140.68861193633</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>1220.46350666454</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>1336.69987984938</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>1335.5373026018</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>1324.17522248478</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>1276.18767138884</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770886</t>
+          <t>1241.75343965884</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>1215.34928600292</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>1137.00312280856</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>1009.74883233058</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>1074.9383020896</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783313</t>
+          <t>1016.9059364978</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>1047.56737192587</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.75272303819012</t>
+          <t>1082.36200755739</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>29427756184.8184</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>30327367379.2327</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>33324846151.3712</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>36569912606.9165</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>37018388721.8392</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>34985959810.8131</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>33791290340.3759</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>33155564116.2183</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>31994854627.3817</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>28683077788.1702</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>25625178202.4728</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>27434629267.1009</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>25682395047.0901</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>26614187461.2003</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>27618985526.3988</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>24266816920.5629</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>25003683489.8294</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>27384875304.6721</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>30290066009.6924</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>30956061872.5527</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.218</t>
+          <t>29242482025.1909</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>28692880749.0791</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>27824463849.2129</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>27577475989.0267</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>24666696870.4647</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>22134794425.6131</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>22815660983.8528</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>21527080084.7105</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>23250816108.6471</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>24277467752.7656</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.723</t>
+          <t>5160939264.25547</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.784</t>
+          <t>5323683889.40328</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.175</t>
+          <t>5939970846.69915</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5.261</t>
+          <t>6279846597.22414</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6.115</t>
+          <t>6062326849.28649</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>6.495</t>
+          <t>5743477785.62222</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6.984</t>
+          <t>5098409591.29684</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>8.152</t>
+          <t>5331100267.00541</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>9.124</t>
+          <t>4417378638.35508</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8.792</t>
+          <t>4016380917.70558</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>8.673</t>
+          <t>3490383776.85967</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>9.489</t>
+          <t>4618968283.24809</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>4155314962.37962</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>9.429</t>
+          <t>3363371352.55318</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>9.525</t>
+          <t>3341517773.63318</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>1442.14006682087</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>1436.76557301099</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>1402.62008879953</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>1399.70043979058</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.706</t>
+          <t>1427.46603039056</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>1423.176201373</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>1401.63412224738</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1418.33843157937</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>1427.62333885366</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.722</t>
+          <t>1410.91082463679</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>4.697</t>
+          <t>1415.75195672663</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>1418.83325855529</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.807</t>
+          <t>1413.98038176034</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>5.004</t>
+          <t>1400.25047011692</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1397.75212874312</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>1439.00627154417</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1433.89711697907</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1400.60945474994</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1397.74395321716</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1424.99138318587</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.981</t>
+          <t>1421.11325920907</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.084</t>
+          <t>1399.87253779959</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.394</t>
+          <t>1416.74032958497</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.642</t>
+          <t>1426.65286423619</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.445</t>
+          <t>1409.98968985831</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.388</t>
+          <t>1414.88080354073</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.574</t>
+          <t>1417.84678989279</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.407</t>
+          <t>1412.93932148601</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.522</t>
+          <t>1399.27207181149</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>1397.02139533861</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>356399.540106134</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>355024.777026633</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>375712.66632429</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>438435.86737551</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>510237.702997729</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>541868.426556212</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>588155.241436866</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>675001.923390472</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>753989.751476986</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>607129.808764642</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>649302.394965377</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>749847.14812032</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>715939.949497564</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>748615.203781869</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>759654.358392825</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9647127393.00506</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9447967962.7216</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9290487473.50986</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>9655819067.01534</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10928118547.0692</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11267386567.6985</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12027173693.1112</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>11941798843.6014</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>12462728698.8455</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>10681160749.0947</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>10989417755.5141</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>12754050741.421</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>11925846331.1901</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>11633293540.9349</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>11526278001.4292</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>329831.907460613</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>326609.724558394</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>339913.617314042</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>403824.903183249</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>481967.996508953</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>530312.143841983</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>584511.729276589</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>679225.805010762</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>766033.202332542</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>616542.499781893</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>666783.421275292</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>788194.997352575</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>742092.888224248</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>769578.359544837</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>776338.465282663</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>36942.169</t>
+          <t>34970159137.6053</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>37340.115</t>
+          <t>35226372743.828</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>36641.344</t>
+          <t>36834661967.9114</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>36570.573</t>
+          <t>40959791695.4925</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>37323.374</t>
+          <t>44045429509.3244</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>37483.283</t>
+          <t>44796190782.8396</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>37330.401</t>
+          <t>45400309241.428</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>38311.492</t>
+          <t>45510461543.7215</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>38757.878</t>
+          <t>45494421883.617</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>37873.733</t>
+          <t>40280562506.0894</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>38048.975</t>
+          <t>38126403695.3844</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>38433.573</t>
+          <t>43335095096.6615</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>38427.711</t>
+          <t>39777079771.1577</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>38056.003</t>
+          <t>39995600730.0705</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>38131.699</t>
+          <t>40522971454.6864</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>33668.202</t>
+          <t>26567.6326455206</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>34113.125</t>
+          <t>28415.052468239</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>33486.152</t>
+          <t>35799.049010248</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>33417.848</t>
+          <t>34610.9641922604</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>34100.736</t>
+          <t>28269.7064887767</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>34206.04</t>
+          <t>11556.2827142297</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>34052.701</t>
+          <t>3643.51216027736</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>34960.624</t>
+          <t>-4223.88162029069</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>35343.671</t>
+          <t>-12043.4508555561</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>34475.606</t>
+          <t>-9412.69101725139</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>34548.595</t>
+          <t>-17481.0263099154</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>34785.535</t>
+          <t>-38347.8492322548</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>34667.971</t>
+          <t>-26152.9387266844</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>34252.927</t>
+          <t>-20963.1557629681</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>34307.826</t>
+          <t>-16684.1068898379</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>46483.444</t>
+          <t>-25323031744.6002</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>45661.444</t>
+          <t>-25778404781.1064</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>44757.307</t>
+          <t>-27544174494.4015</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>46825.718</t>
+          <t>-31303972628.4771</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>50016.414</t>
+          <t>-33117310962.2552</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>50211.829</t>
+          <t>-33528804215.1411</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>51228.355</t>
+          <t>-33373135548.3169</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>52340.881</t>
+          <t>-33568662700.1201</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>53256.369</t>
+          <t>-33031693184.7715</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>50438.75</t>
+          <t>-29599401756.9947</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>49250.502</t>
+          <t>-27136985939.8703</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>54656.043</t>
+          <t>-30581044355.2405</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>51138.873</t>
+          <t>-27851233439.9676</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>49086.517</t>
+          <t>-28362307189.1357</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>48477.493</t>
+          <t>-28996693453.2572</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>500328.8976</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>502711.9228</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>547985.6016</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>665758.7104</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>759945.7782</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>779085.2784</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>810403.1636</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>929075.655</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>1018448.106</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>937784.0164</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>915778.9773</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>991798.608</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>928647.016</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>972772.1574</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>978634.061239337</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16971.508</t>
+          <t>0.0679327297095382</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16961.326</t>
+          <t>0.0673026194168773</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16550.12</t>
+          <t>0.0648877524394552</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>16487.799</t>
+          <t>0.0619962272446338</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>16807.7</t>
+          <t>0.0624445792824497</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16837.287</t>
+          <t>0.0593538675152681</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>16764.231</t>
+          <t>0.0571377536645254</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>17147.916</t>
+          <t>0.0582244632953005</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>17355.462</t>
+          <t>0.0561890165277656</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>16975.156</t>
+          <t>0.0450569506917461</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16917.761</t>
+          <t>0.0420164301273508</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>17015.951</t>
+          <t>0.0401626785588858</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>16935.501</t>
+          <t>0.036354250170645</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>16743.292</t>
+          <t>0.0358294133669148</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>16729.787</t>
+          <t>0.0334356569429454</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>694092.327</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>703433.7948</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>773290.404</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>952155.13456</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>1083643.01423</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>1123623.96861</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>1182790.76944</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1342996.66895</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1485794.806</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>1412950.5324</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>1379009.0484</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>1487949.168</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>1403458.9888</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>1470227.9496</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>1495258.36790236</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>26374.426</t>
+          <t>751937.76444</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>27086.414</t>
+          <t>760865.4882</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>29140.802</t>
+          <t>836796.14352</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31916.306</t>
+          <t>1031001.132</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>31905.036</t>
+          <t>1173619.15244</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>31828.395</t>
+          <t>1218458.35254</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>31006.372</t>
+          <t>1283976.18332</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>30612.596</t>
+          <t>1457851.8326</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>30091.824</t>
+          <t>1613747.19908</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>27784.965</t>
+          <t>1536154.05328</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>24643.317</t>
+          <t>1504369.22895</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>26356.799</t>
+          <t>1629203.4816</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>24932.529</t>
+          <t>1542504.5416</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>25623.886</t>
+          <t>1621123.21854</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>26563.515</t>
+          <t>1648332.55918132</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>3722862.5812</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>3783614.4537912</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>4175276.9414544</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5260731.5712</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6115391.7882561</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>6495303.0272559</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>6984335.2662888</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>8151868.3076295</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>9124454.9088</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>8791590.3825948</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>8673233.1633486</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>9489138.721392</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>8979715.172824</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>33.68</t>
+          <t>9429114.2208876</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>9524999.86811111</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>920546.710797266</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>934647.274504707</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>950777.868759905</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>956381.223075434</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>975617.55974016</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>994559.299232646</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>1021920.51079015</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1036539.54343884</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>1046882.58768027</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>1033769.71040605</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>1048076.8046</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>1076178.99613584</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>1093802.45980631</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>1102430.56625954</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>1118178.95682089</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>848559.257065481</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>864018.443625761</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>878420.405688407</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>884191.181078976</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>900813.628131529</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>917423.454253822</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>941407.414518992</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>956334.822033479</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>965303.565684027</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>949393.299483539</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>960739.8032</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>983413.384616015</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>997039.485765142</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1000618.19279852</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1014667.69707038</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>479278.29876</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>484416.1582</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>521698.11072</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>638661.04064</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>741280.31236</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>762347.77905</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>799794.97588</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>936166.21085</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1028214.07092</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>908539.80272</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>883199.23695</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>945294.8112</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>864502.7336</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>901364.86875</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>889410.788649521</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>33668202000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34113125000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>33486152000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>33417848000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>34100736000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>34206040000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>34052701000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>34960624000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>35343671000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>34475606000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>34548595000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>34785535000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>34667971000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>34252927000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>34307826000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>36942169003.0818</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>37340114823.252</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>36641343945.7132</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>36570572791.9737</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>37323374308.4042</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>37483283324.8983</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>37330400965.5017</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>38311491992.6367</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>38757878362.7045</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>37873733059.2841</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>38048974568.8174</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>38433572933.6238</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>38427710726.4551</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>38056002537.057</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>38131698985.7674</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>16971508241.1957</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16961325891.697</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>16550120075.9172</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>16487799472.8652</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>16807699721.342</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>16837287190.2714</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>16764231327.4608</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>17147916327.4675</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>17355462181.8256</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>16975156000.752</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>16917761498.2304</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>17015950771.2338</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>16935500675.4427</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>16743292474.491</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>16729787239.6784</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>25672000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>26041000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>26161000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>26164000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>26192000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>26376000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>26667000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>27042000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>27167000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>26861000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>26892000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>27107000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>27197000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>27197000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>27295000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>23346000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>23743000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>23874000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>23875000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>23889000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>24035000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>24295000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>24649000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>24757000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>24435000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>24403000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>24517000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>24518000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>24462000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>24545000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>36942169003.0818</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>37340114823.252</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>36641343945.7132</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>36570572791.9737</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>37323374308.4042</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>37483283324.8983</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>37330400965.5017</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>38311491992.6367</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>38757878362.7045</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>37873733059.2841</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>38048974568.8174</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>38433572933.6238</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>38427710726.4551</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>38056002537.057</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>38131698985.7674</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>33668202000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>34113125000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>33486152000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>33417848000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>34100736000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>34206040000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>34052701000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>34960624000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>35343671000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>34475606000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>34548595000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>34785535000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>34667971000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>34252927000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>34307826000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2414723.5684</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2451820.5324</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2646301.3152</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3221789.9504</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3706355.5375</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3875851.7226</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4128007.2412</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4749697.994</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5251791.4432</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4721921.05</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>4696735.0338</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>5130046.176</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4806515.1728</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5004462.7497</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>5020134.47832235</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1231216.0632</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1245281.6464</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1358494.3488</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1669662.512</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1914899.4648</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1980806.256</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2083771.1592</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2394018.1805</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2641961.27</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2444693.856</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2387568.4659</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2574498.432</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2407007.2752</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2522488.2201</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2537743.21407052</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4764983.10070951</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4875586.5233242</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4966181.93358667</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5103526.60505274</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5253743.73592781</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5401171.36697318</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5580475.43250371</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5787142.46993164</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>5896142.42550277</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5914135.56708469</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>6042542.1661528</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>6217741.152499</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>6283610.2018104</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>6360583.42120331</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>6394626.84816393</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
